--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1685"/>
+  <dimension ref="A1:C1688"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18922,6 +18922,39 @@
         <v>450.91</v>
       </c>
     </row>
+    <row r="1686" spans="1:3">
+      <c r="A1686" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B1686">
+        <v>1</v>
+      </c>
+      <c r="C1686">
+        <v>450.91</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:3">
+      <c r="A1687" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B1687">
+        <v>1</v>
+      </c>
+      <c r="C1687">
+        <v>450.91</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:3">
+      <c r="A1688" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B1688">
+        <v>1</v>
+      </c>
+      <c r="C1688">
+        <v>447.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1688"/>
+  <dimension ref="A1:C1689"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18955,6 +18955,17 @@
         <v>447.8</v>
       </c>
     </row>
+    <row r="1689" spans="1:3">
+      <c r="A1689" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B1689">
+        <v>1</v>
+      </c>
+      <c r="C1689">
+        <v>447.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1689"/>
+  <dimension ref="A1:C1690"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18966,6 +18966,17 @@
         <v>447.88</v>
       </c>
     </row>
+    <row r="1690" spans="1:3">
+      <c r="A1690" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B1690">
+        <v>1</v>
+      </c>
+      <c r="C1690">
+        <v>444.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1690"/>
+  <dimension ref="A1:C1691"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18977,6 +18977,17 @@
         <v>444.88</v>
       </c>
     </row>
+    <row r="1691" spans="1:3">
+      <c r="A1691" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B1691">
+        <v>1</v>
+      </c>
+      <c r="C1691">
+        <v>444.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1691"/>
+  <dimension ref="A1:C1692"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18988,6 +18988,17 @@
         <v>444.58</v>
       </c>
     </row>
+    <row r="1692" spans="1:3">
+      <c r="A1692" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1692">
+        <v>1</v>
+      </c>
+      <c r="C1692">
+        <v>446.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1692"/>
+  <dimension ref="A1:C1695"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18999,6 +18999,39 @@
         <v>446.56</v>
       </c>
     </row>
+    <row r="1693" spans="1:3">
+      <c r="A1693" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1693">
+        <v>1</v>
+      </c>
+      <c r="C1693">
+        <v>446.56</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:3">
+      <c r="A1694" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1694">
+        <v>1</v>
+      </c>
+      <c r="C1694">
+        <v>446.56</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:3">
+      <c r="A1695" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1695">
+        <v>1</v>
+      </c>
+      <c r="C1695">
+        <v>448.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1695"/>
+  <dimension ref="A1:C1696"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19032,6 +19032,17 @@
         <v>448.44</v>
       </c>
     </row>
+    <row r="1696" spans="1:3">
+      <c r="A1696" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B1696">
+        <v>1</v>
+      </c>
+      <c r="C1696">
+        <v>447.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1696"/>
+  <dimension ref="A1:C1697"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19043,6 +19043,17 @@
         <v>447.85</v>
       </c>
     </row>
+    <row r="1697" spans="1:3">
+      <c r="A1697" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B1697">
+        <v>1</v>
+      </c>
+      <c r="C1697">
+        <v>445.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1697"/>
+  <dimension ref="A1:C1698"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19054,6 +19054,17 @@
         <v>445.65</v>
       </c>
     </row>
+    <row r="1698" spans="1:3">
+      <c r="A1698" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B1698">
+        <v>1</v>
+      </c>
+      <c r="C1698">
+        <v>441.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1698"/>
+  <dimension ref="A1:C1699"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19065,6 +19065,17 @@
         <v>441.89</v>
       </c>
     </row>
+    <row r="1699" spans="1:3">
+      <c r="A1699" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B1699">
+        <v>1</v>
+      </c>
+      <c r="C1699">
+        <v>441.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1699"/>
+  <dimension ref="A1:C1702"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19076,6 +19076,39 @@
         <v>441.88</v>
       </c>
     </row>
+    <row r="1700" spans="1:3">
+      <c r="A1700" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B1700">
+        <v>1</v>
+      </c>
+      <c r="C1700">
+        <v>441.88</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:3">
+      <c r="A1701" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B1701">
+        <v>1</v>
+      </c>
+      <c r="C1701">
+        <v>441.88</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:3">
+      <c r="A1702" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B1702">
+        <v>1</v>
+      </c>
+      <c r="C1702">
+        <v>441.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1702"/>
+  <dimension ref="A1:C1703"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19109,6 +19109,17 @@
         <v>441.77</v>
       </c>
     </row>
+    <row r="1703" spans="1:3">
+      <c r="A1703" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B1703">
+        <v>1</v>
+      </c>
+      <c r="C1703">
+        <v>439.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1703"/>
+  <dimension ref="A1:C1704"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19120,6 +19120,17 @@
         <v>439.37</v>
       </c>
     </row>
+    <row r="1704" spans="1:3">
+      <c r="A1704" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B1704">
+        <v>1</v>
+      </c>
+      <c r="C1704">
+        <v>440.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1704"/>
+  <dimension ref="A1:C1705"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19131,6 +19131,17 @@
         <v>440.86</v>
       </c>
     </row>
+    <row r="1705" spans="1:3">
+      <c r="A1705" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B1705">
+        <v>1</v>
+      </c>
+      <c r="C1705">
+        <v>441.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1705"/>
+  <dimension ref="A1:C1706"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19142,6 +19142,17 @@
         <v>441.91</v>
       </c>
     </row>
+    <row r="1706" spans="1:3">
+      <c r="A1706" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B1706">
+        <v>1</v>
+      </c>
+      <c r="C1706">
+        <v>447.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1706"/>
+  <dimension ref="A1:C1709"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19153,6 +19153,39 @@
         <v>447.73</v>
       </c>
     </row>
+    <row r="1707" spans="1:3">
+      <c r="A1707" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B1707">
+        <v>1</v>
+      </c>
+      <c r="C1707">
+        <v>447.73</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:3">
+      <c r="A1708" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B1708">
+        <v>1</v>
+      </c>
+      <c r="C1708">
+        <v>447.73</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:3">
+      <c r="A1709" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B1709">
+        <v>1</v>
+      </c>
+      <c r="C1709">
+        <v>454.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1709"/>
+  <dimension ref="A1:C1710"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19186,6 +19186,17 @@
         <v>454.98</v>
       </c>
     </row>
+    <row r="1710" spans="1:3">
+      <c r="A1710" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B1710">
+        <v>1</v>
+      </c>
+      <c r="C1710">
+        <v>453.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1710"/>
+  <dimension ref="A1:C1711"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19197,6 +19197,17 @@
         <v>453.65</v>
       </c>
     </row>
+    <row r="1711" spans="1:3">
+      <c r="A1711" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B1711">
+        <v>1</v>
+      </c>
+      <c r="C1711">
+        <v>447.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1711"/>
+  <dimension ref="A1:C1712"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19208,6 +19208,17 @@
         <v>447.14</v>
       </c>
     </row>
+    <row r="1712" spans="1:3">
+      <c r="A1712" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B1712">
+        <v>1</v>
+      </c>
+      <c r="C1712">
+        <v>448.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1712"/>
+  <dimension ref="A1:C1713"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19219,6 +19219,17 @@
         <v>448.94</v>
       </c>
     </row>
+    <row r="1713" spans="1:3">
+      <c r="A1713" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B1713">
+        <v>1</v>
+      </c>
+      <c r="C1713">
+        <v>453.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1713"/>
+  <dimension ref="A1:C1716"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19230,6 +19230,39 @@
         <v>453.93</v>
       </c>
     </row>
+    <row r="1714" spans="1:3">
+      <c r="A1714" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1714">
+        <v>1</v>
+      </c>
+      <c r="C1714">
+        <v>453.93</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:3">
+      <c r="A1715" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1715">
+        <v>1</v>
+      </c>
+      <c r="C1715">
+        <v>453.93</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:3">
+      <c r="A1716" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1716">
+        <v>1</v>
+      </c>
+      <c r="C1716">
+        <v>451.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1716"/>
+  <dimension ref="A1:C1717"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19263,6 +19263,17 @@
         <v>451.31</v>
       </c>
     </row>
+    <row r="1717" spans="1:3">
+      <c r="A1717" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1717">
+        <v>1</v>
+      </c>
+      <c r="C1717">
+        <v>448.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1717"/>
+  <dimension ref="A1:C1718"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19274,6 +19274,17 @@
         <v>448.45</v>
       </c>
     </row>
+    <row r="1718" spans="1:3">
+      <c r="A1718" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1718">
+        <v>1</v>
+      </c>
+      <c r="C1718">
+        <v>450.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1718"/>
+  <dimension ref="A1:C1719"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19285,6 +19285,17 @@
         <v>450.62</v>
       </c>
     </row>
+    <row r="1719" spans="1:3">
+      <c r="A1719" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1719">
+        <v>1</v>
+      </c>
+      <c r="C1719">
+        <v>454.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1719"/>
+  <dimension ref="A1:C1720"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19296,6 +19296,17 @@
         <v>454.14</v>
       </c>
     </row>
+    <row r="1720" spans="1:3">
+      <c r="A1720" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1720">
+        <v>1</v>
+      </c>
+      <c r="C1720">
+        <v>452.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1720"/>
+  <dimension ref="A1:C1723"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19307,6 +19307,39 @@
         <v>452.12</v>
       </c>
     </row>
+    <row r="1721" spans="1:3">
+      <c r="A1721" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1721">
+        <v>1</v>
+      </c>
+      <c r="C1721">
+        <v>452.12</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:3">
+      <c r="A1722" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1722">
+        <v>1</v>
+      </c>
+      <c r="C1722">
+        <v>452.12</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1723">
+        <v>1</v>
+      </c>
+      <c r="C1723">
+        <v>452.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1723"/>
+  <dimension ref="A1:C1724"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19340,6 +19340,17 @@
         <v>452.59</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1724">
+        <v>1</v>
+      </c>
+      <c r="C1724">
+        <v>450.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1724"/>
+  <dimension ref="A1:C1725"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19351,6 +19351,17 @@
         <v>450.69</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B1725">
+        <v>1</v>
+      </c>
+      <c r="C1725">
+        <v>448.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1725"/>
+  <dimension ref="A1:C1726"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19362,6 +19362,17 @@
         <v>448.61</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B1726">
+        <v>1</v>
+      </c>
+      <c r="C1726">
+        <v>447.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1726"/>
+  <dimension ref="A1:C1727"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19373,6 +19373,17 @@
         <v>447.94</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B1727">
+        <v>1</v>
+      </c>
+      <c r="C1727">
+        <v>451.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1727"/>
+  <dimension ref="A1:C1730"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19384,6 +19384,39 @@
         <v>451.05</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B1728">
+        <v>1</v>
+      </c>
+      <c r="C1728">
+        <v>451.05</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B1729">
+        <v>1</v>
+      </c>
+      <c r="C1729">
+        <v>451.05</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B1730">
+        <v>1</v>
+      </c>
+      <c r="C1730">
+        <v>451.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1730"/>
+  <dimension ref="A1:C1731"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19417,6 +19417,17 @@
         <v>451.05</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B1731">
+        <v>1</v>
+      </c>
+      <c r="C1731">
+        <v>455.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1731"/>
+  <dimension ref="A1:C1732"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19428,6 +19428,17 @@
         <v>455.63</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B1732">
+        <v>1</v>
+      </c>
+      <c r="C1732">
+        <v>457.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1732"/>
+  <dimension ref="A1:C1733"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19439,6 +19439,17 @@
         <v>457.09</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B1733">
+        <v>1</v>
+      </c>
+      <c r="C1733">
+        <v>453.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/nbk/data/nbk_tenge.xlsx
+++ b/LME/parser/nbk/data/nbk_tenge.xlsx
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1733"/>
+  <dimension ref="A1:C1734"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19450,6 +19450,17 @@
         <v>453.71</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="2">
+        <v>46326</v>
+      </c>
+      <c r="B1734">
+        <v>1</v>
+      </c>
+      <c r="C1734">
+        <v>453.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
